--- a/woordverificatie woordenlijst.org.xlsx
+++ b/woordverificatie woordenlijst.org.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Business\AI\Woordenlijstchecker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14840B2-B9FF-4407-BBA9-E43F899585C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F90028-161A-4DC6-8CC3-158457979B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{81616EE2-043F-4D22-B1B2-F464E628B82B}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{81616EE2-043F-4D22-B1B2-F464E628B82B}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="105">
   <si>
     <t>term</t>
   </si>
@@ -345,6 +345,12 @@
   </si>
   <si>
     <t>znw. mv.</t>
+  </si>
+  <si>
+    <t>* 2 of meer ww worden geteld als 1</t>
+  </si>
+  <si>
+    <t>* CdK heeft twee exact gelijke ingangen</t>
   </si>
 </sst>
 </file>
@@ -725,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7FBE9A9-D5DA-4E23-9A2E-16455A247FB8}">
-  <dimension ref="A1:W67"/>
+  <dimension ref="A1:W81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5546875" customWidth="1"/>
@@ -898,10 +904,13 @@
         <v>1</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q4">
         <v>2</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
       </c>
       <c r="W4">
         <f>SUM(B4:U4)</f>
@@ -1054,14 +1063,17 @@
         <v>1</v>
       </c>
       <c r="P14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q14">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
       </c>
       <c r="W14">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
@@ -1266,12 +1278,9 @@
       <c r="Q30">
         <v>1</v>
       </c>
-      <c r="S30">
-        <v>1</v>
-      </c>
       <c r="W30">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.3">
@@ -1287,9 +1296,12 @@
       <c r="A32" t="s">
         <v>37</v>
       </c>
+      <c r="T32">
+        <v>1</v>
+      </c>
       <c r="W32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.3">
@@ -1368,7 +1380,7 @@
       <c r="A40" t="s">
         <v>45</v>
       </c>
-      <c r="Q40">
+      <c r="R40">
         <v>1</v>
       </c>
       <c r="W40">
@@ -1516,10 +1528,13 @@
         <v>57</v>
       </c>
       <c r="P52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q52">
         <v>2</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
       </c>
       <c r="W52">
         <f t="shared" si="0"/>
@@ -1560,9 +1575,12 @@
       <c r="A55" t="s">
         <v>60</v>
       </c>
+      <c r="R55">
+        <v>1</v>
+      </c>
       <c r="W55">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.3">
@@ -1704,6 +1722,16 @@
       <c r="W67">
         <f t="shared" si="0"/>
         <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/woordverificatie woordenlijst.org.xlsx
+++ b/woordverificatie woordenlijst.org.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Business\AI\Woordenlijstchecker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F90028-161A-4DC6-8CC3-158457979B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A45424-493D-491F-8914-4BB7258CA938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{81616EE2-043F-4D22-B1B2-F464E628B82B}"/>
   </bookViews>
@@ -904,13 +904,10 @@
         <v>1</v>
       </c>
       <c r="P4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4">
         <v>2</v>
-      </c>
-      <c r="R4">
-        <v>1</v>
       </c>
       <c r="W4">
         <f>SUM(B4:U4)</f>
@@ -1068,12 +1065,9 @@
       <c r="Q14">
         <v>1</v>
       </c>
-      <c r="R14">
-        <v>1</v>
-      </c>
       <c r="W14">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
@@ -1296,7 +1290,7 @@
       <c r="A32" t="s">
         <v>37</v>
       </c>
-      <c r="T32">
+      <c r="S32">
         <v>1</v>
       </c>
       <c r="W32">
@@ -1533,12 +1527,9 @@
       <c r="Q52">
         <v>2</v>
       </c>
-      <c r="R52">
-        <v>1</v>
-      </c>
       <c r="W52">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.3">
